--- a/test/data/example.xlsx
+++ b/test/data/example.xlsx
@@ -47,7 +47,7 @@
     <t>License plate</t>
   </si>
   <si>
-    <t>Marke</t>
+    <t>Brand</t>
   </si>
   <si>
     <t>Modell</t>
